--- a/MAJSushiConfig/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-care-plan-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-care-plan-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1170,7 +1170,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1484,7 +1484,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
+Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
   </si>
   <si>
     <t>Produit de santé</t>
